--- a/docs/user-guide/screenshots/all-pages/export-excel.xlsx
+++ b/docs/user-guide/screenshots/all-pages/export-excel.xlsx
@@ -477,7 +477,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ingrediente 7ec03f12</t>
+          <t>Ingrediente ac7a9c2a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Receta 2f6bbb5d</t>
+          <t>Receta 3117c905</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -682,7 +682,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Receta 2f6bbb5d</t>
+          <t>Receta 3117c905</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ingrediente 7ec03f12</t>
+          <t>Ingrediente ac7a9c2a</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -797,7 +797,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Producto 5bf8a725</t>
+          <t>Producto 7e132b24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Receta 2f6bbb5d</t>
+          <t>Receta 3117c905</t>
         </is>
       </c>
     </row>
@@ -999,14 +999,14 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46287.84018083566</v>
+        <v>46287.87390256486</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Producto 5bf8a725</t>
+          <t>Producto 7e132b24</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -1023,14 +1023,14 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46288.17351416899</v>
+        <v>46288.2072358982</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Producto 5bf8a725</t>
+          <t>Producto 7e132b24</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -1047,14 +1047,14 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46288.50684750233</v>
+        <v>46288.54056923153</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Producto 5bf8a725</t>
+          <t>Producto 7e132b24</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1071,14 +1071,14 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46288.84018083566</v>
+        <v>46288.87390256486</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Producto 5bf8a725</t>
+          <t>Producto 7e132b24</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1095,14 +1095,14 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46289.17351416899</v>
+        <v>46289.2072358982</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Producto 5bf8a725</t>
+          <t>Producto 7e132b24</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1119,14 +1119,14 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46289.50684750233</v>
+        <v>46289.54056923153</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Producto 5bf8a725</t>
+          <t>Producto 7e132b24</t>
         </is>
       </c>
       <c r="E7" t="n">

--- a/docs/user-guide/screenshots/all-pages/export-excel.xlsx
+++ b/docs/user-guide/screenshots/all-pages/export-excel.xlsx
@@ -477,7 +477,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ingrediente ac7a9c2a</t>
+          <t>Ingrediente f910ed0e</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Receta 3117c905</t>
+          <t>Receta dd5d03e8</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -682,7 +682,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Receta 3117c905</t>
+          <t>Receta dd5d03e8</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ingrediente ac7a9c2a</t>
+          <t>Ingrediente f910ed0e</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -797,7 +797,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Producto 7e132b24</t>
+          <t>Producto 4d6e202a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Receta 3117c905</t>
+          <t>Receta dd5d03e8</t>
         </is>
       </c>
     </row>
@@ -999,14 +999,14 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46287.87390256486</v>
+        <v>46287.9705130111</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Producto 7e132b24</t>
+          <t>Producto 4d6e202a</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -1023,14 +1023,14 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46288.2072358982</v>
+        <v>46288.30384634443</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Producto 7e132b24</t>
+          <t>Producto 4d6e202a</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -1047,14 +1047,14 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46288.54056923153</v>
+        <v>46288.63717967777</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Producto 7e132b24</t>
+          <t>Producto 4d6e202a</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1071,14 +1071,14 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46288.87390256486</v>
+        <v>46288.9705130111</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Producto 7e132b24</t>
+          <t>Producto 4d6e202a</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1095,14 +1095,14 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46289.2072358982</v>
+        <v>46289.30384634443</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Producto 7e132b24</t>
+          <t>Producto 4d6e202a</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1119,14 +1119,14 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46289.54056923153</v>
+        <v>46289.63717967777</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Producto 7e132b24</t>
+          <t>Producto 4d6e202a</t>
         </is>
       </c>
       <c r="E7" t="n">

--- a/docs/user-guide/screenshots/all-pages/export-excel.xlsx
+++ b/docs/user-guide/screenshots/all-pages/export-excel.xlsx
@@ -477,7 +477,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ingrediente f910ed0e</t>
+          <t>Ingrediente 038f06df</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Receta dd5d03e8</t>
+          <t>Receta 5ea80280</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -682,7 +682,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Receta dd5d03e8</t>
+          <t>Receta 5ea80280</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ingrediente f910ed0e</t>
+          <t>Ingrediente 038f06df</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -797,7 +797,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Producto 4d6e202a</t>
+          <t>Producto d02a8eb4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Receta dd5d03e8</t>
+          <t>Receta 5ea80280</t>
         </is>
       </c>
     </row>
@@ -999,14 +999,14 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46287.9705130111</v>
+        <v>46288.22342887763</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Producto 4d6e202a</t>
+          <t>Producto d02a8eb4</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -1023,14 +1023,14 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46288.30384634443</v>
+        <v>46288.55676221096</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Producto 4d6e202a</t>
+          <t>Producto d02a8eb4</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -1047,14 +1047,14 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46288.63717967777</v>
+        <v>46288.8900955443</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Producto 4d6e202a</t>
+          <t>Producto d02a8eb4</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1071,14 +1071,14 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46288.9705130111</v>
+        <v>46289.22342887763</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Producto 4d6e202a</t>
+          <t>Producto d02a8eb4</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1095,14 +1095,14 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46289.30384634443</v>
+        <v>46289.55676221096</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Producto 4d6e202a</t>
+          <t>Producto d02a8eb4</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1119,14 +1119,14 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46289.63717967777</v>
+        <v>46289.8900955443</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Producto 4d6e202a</t>
+          <t>Producto d02a8eb4</t>
         </is>
       </c>
       <c r="E7" t="n">

--- a/docs/user-guide/screenshots/all-pages/export-excel.xlsx
+++ b/docs/user-guide/screenshots/all-pages/export-excel.xlsx
@@ -477,7 +477,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ingrediente 038f06df</t>
+          <t>Ingrediente cb3902ac</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Receta 5ea80280</t>
+          <t>Receta e2d0d7f1</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -682,7 +682,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Receta 5ea80280</t>
+          <t>Receta e2d0d7f1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ingrediente 038f06df</t>
+          <t>Ingrediente cb3902ac</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -797,7 +797,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Producto d02a8eb4</t>
+          <t>Producto 82181abe</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Receta 5ea80280</t>
+          <t>Receta e2d0d7f1</t>
         </is>
       </c>
     </row>
@@ -999,14 +999,14 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46288.22342887763</v>
+        <v>46288.26570425607</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Producto d02a8eb4</t>
+          <t>Producto 82181abe</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -1023,14 +1023,14 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46288.55676221096</v>
+        <v>46288.59903758941</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Producto d02a8eb4</t>
+          <t>Producto 82181abe</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -1047,14 +1047,14 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46288.8900955443</v>
+        <v>46288.93237092275</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Producto d02a8eb4</t>
+          <t>Producto 82181abe</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1071,14 +1071,14 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46289.22342887763</v>
+        <v>46289.26570425607</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Producto d02a8eb4</t>
+          <t>Producto 82181abe</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1095,14 +1095,14 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46289.55676221096</v>
+        <v>46289.59903758941</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Producto d02a8eb4</t>
+          <t>Producto 82181abe</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1119,14 +1119,14 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46289.8900955443</v>
+        <v>46289.93237092275</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Producto d02a8eb4</t>
+          <t>Producto 82181abe</t>
         </is>
       </c>
       <c r="E7" t="n">

--- a/docs/user-guide/screenshots/all-pages/export-excel.xlsx
+++ b/docs/user-guide/screenshots/all-pages/export-excel.xlsx
@@ -477,7 +477,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ingrediente cb3902ac</t>
+          <t>Ingrediente 59446791</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Receta e2d0d7f1</t>
+          <t>Receta 7dab5b64</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -682,7 +682,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Receta e2d0d7f1</t>
+          <t>Receta 7dab5b64</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ingrediente cb3902ac</t>
+          <t>Ingrediente 59446791</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -797,7 +797,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Producto 82181abe</t>
+          <t>Producto 27078bf6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Receta e2d0d7f1</t>
+          <t>Receta 7dab5b64</t>
         </is>
       </c>
     </row>
@@ -999,14 +999,14 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46288.26570425607</v>
+        <v>46288.29523119341</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Producto 82181abe</t>
+          <t>Producto 27078bf6</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -1023,14 +1023,14 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46288.59903758941</v>
+        <v>46288.62856452673</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Producto 82181abe</t>
+          <t>Producto 27078bf6</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -1047,14 +1047,14 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46288.93237092275</v>
+        <v>46288.96189786007</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Producto 82181abe</t>
+          <t>Producto 27078bf6</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1071,14 +1071,14 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46289.26570425607</v>
+        <v>46289.29523119341</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Producto 82181abe</t>
+          <t>Producto 27078bf6</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1095,14 +1095,14 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46289.59903758941</v>
+        <v>46289.62856452673</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Producto 82181abe</t>
+          <t>Producto 27078bf6</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1119,14 +1119,14 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46289.93237092275</v>
+        <v>46289.96189786007</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Producto 82181abe</t>
+          <t>Producto 27078bf6</t>
         </is>
       </c>
       <c r="E7" t="n">

--- a/docs/user-guide/screenshots/all-pages/export-excel.xlsx
+++ b/docs/user-guide/screenshots/all-pages/export-excel.xlsx
@@ -477,7 +477,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ingrediente 59446791</t>
+          <t>Ingrediente 9551f65b</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Receta 7dab5b64</t>
+          <t>Receta 0e8c932f</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -682,7 +682,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Receta 7dab5b64</t>
+          <t>Receta 0e8c932f</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ingrediente 59446791</t>
+          <t>Ingrediente 9551f65b</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -797,7 +797,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Producto 27078bf6</t>
+          <t>Producto 1aacee13</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Receta 7dab5b64</t>
+          <t>Receta 0e8c932f</t>
         </is>
       </c>
     </row>
@@ -999,14 +999,14 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46288.29523119341</v>
+        <v>46288.86658869901</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Producto 27078bf6</t>
+          <t>Producto 1aacee13</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -1023,14 +1023,14 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46288.62856452673</v>
+        <v>46289.19992203234</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Producto 27078bf6</t>
+          <t>Producto 1aacee13</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -1047,14 +1047,14 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46288.96189786007</v>
+        <v>46289.53325536567</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Producto 27078bf6</t>
+          <t>Producto 1aacee13</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1071,14 +1071,14 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46289.29523119341</v>
+        <v>46289.86658869901</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Producto 27078bf6</t>
+          <t>Producto 1aacee13</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1095,14 +1095,14 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46289.62856452673</v>
+        <v>46290.19992203234</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Producto 27078bf6</t>
+          <t>Producto 1aacee13</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1119,14 +1119,14 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46289.96189786007</v>
+        <v>46290.53325536567</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Producto 27078bf6</t>
+          <t>Producto 1aacee13</t>
         </is>
       </c>
       <c r="E7" t="n">

--- a/docs/user-guide/screenshots/all-pages/export-excel.xlsx
+++ b/docs/user-guide/screenshots/all-pages/export-excel.xlsx
@@ -477,7 +477,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ingrediente 9551f65b</t>
+          <t>Ingrediente 37f13e51</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Receta 0e8c932f</t>
+          <t>Receta d6c29c89</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -682,7 +682,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Receta 0e8c932f</t>
+          <t>Receta d6c29c89</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ingrediente 9551f65b</t>
+          <t>Ingrediente 37f13e51</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -797,7 +797,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Producto 1aacee13</t>
+          <t>Producto 5f9b1800</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Receta 0e8c932f</t>
+          <t>Receta d6c29c89</t>
         </is>
       </c>
     </row>
@@ -999,14 +999,14 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46288.86658869901</v>
+        <v>46288.99773483026</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Producto 1aacee13</t>
+          <t>Producto 5f9b1800</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -1023,14 +1023,14 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46289.19992203234</v>
+        <v>46289.3310681636</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Producto 1aacee13</t>
+          <t>Producto 5f9b1800</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -1047,14 +1047,14 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46289.53325536567</v>
+        <v>46289.66440149694</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Producto 1aacee13</t>
+          <t>Producto 5f9b1800</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1071,14 +1071,14 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46289.86658869901</v>
+        <v>46289.99773483026</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Producto 1aacee13</t>
+          <t>Producto 5f9b1800</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1095,14 +1095,14 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46290.19992203234</v>
+        <v>46290.3310681636</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Producto 1aacee13</t>
+          <t>Producto 5f9b1800</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1119,14 +1119,14 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46290.53325536567</v>
+        <v>46290.66440149694</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Producto 1aacee13</t>
+          <t>Producto 5f9b1800</t>
         </is>
       </c>
       <c r="E7" t="n">

--- a/docs/user-guide/screenshots/all-pages/export-excel.xlsx
+++ b/docs/user-guide/screenshots/all-pages/export-excel.xlsx
@@ -477,7 +477,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ingrediente 37f13e51</t>
+          <t>Ingrediente 840b0455</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Receta d6c29c89</t>
+          <t>Receta 33e39a87</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -682,7 +682,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Receta d6c29c89</t>
+          <t>Receta 33e39a87</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ingrediente 37f13e51</t>
+          <t>Ingrediente 840b0455</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -797,7 +797,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Producto 5f9b1800</t>
+          <t>Producto 0faba1b0</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Receta d6c29c89</t>
+          <t>Receta 33e39a87</t>
         </is>
       </c>
     </row>
@@ -999,14 +999,14 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46288.99773483026</v>
+        <v>46289.29964811084</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Producto 5f9b1800</t>
+          <t>Producto 0faba1b0</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -1023,14 +1023,14 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46289.3310681636</v>
+        <v>46289.63298144418</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Producto 5f9b1800</t>
+          <t>Producto 0faba1b0</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -1047,14 +1047,14 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46289.66440149694</v>
+        <v>46289.96631477751</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Producto 5f9b1800</t>
+          <t>Producto 0faba1b0</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1071,14 +1071,14 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46289.99773483026</v>
+        <v>46290.29964811084</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Producto 5f9b1800</t>
+          <t>Producto 0faba1b0</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1095,14 +1095,14 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46290.3310681636</v>
+        <v>46290.63298144418</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Producto 5f9b1800</t>
+          <t>Producto 0faba1b0</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1119,14 +1119,14 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46290.66440149694</v>
+        <v>46290.96631477751</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Producto 5f9b1800</t>
+          <t>Producto 0faba1b0</t>
         </is>
       </c>
       <c r="E7" t="n">
